--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>fcf_yield</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -526,6 +541,15 @@
       <c r="L2" t="n">
         <v>0.91</v>
       </c>
+      <c r="M2" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>68904</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +593,15 @@
       </c>
       <c r="L3" t="n">
         <v>0.05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4270</v>
       </c>
     </row>
     <row r="4">
@@ -612,6 +645,15 @@
       <c r="L4" t="n">
         <v>0.78</v>
       </c>
+      <c r="M4" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50351</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -656,6 +698,15 @@
       <c r="L5" t="n">
         <v>0.13</v>
       </c>
+      <c r="M5" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>35517</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -700,6 +751,15 @@
       <c r="L6" t="n">
         <v>8.289999999999999</v>
       </c>
+      <c r="M6" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>240893</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -744,6 +804,15 @@
       <c r="L7" t="n">
         <v>0.15</v>
       </c>
+      <c r="M7" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12375</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,6 +857,15 @@
       <c r="L8" t="n">
         <v>0.17</v>
       </c>
+      <c r="M8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>35495</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -832,6 +910,15 @@
       <c r="L9" t="n">
         <v>1.22</v>
       </c>
+      <c r="M9" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26711</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -876,6 +963,15 @@
       <c r="L10" t="n">
         <v>0.85</v>
       </c>
+      <c r="M10" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>48497</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -920,6 +1016,15 @@
       <c r="L11" t="n">
         <v>0.59</v>
       </c>
+      <c r="M11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12383</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -964,6 +1069,15 @@
       <c r="L12" t="n">
         <v>3.84</v>
       </c>
+      <c r="M12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>109913</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1008,6 +1122,15 @@
       <c r="L13" t="n">
         <v>1.81</v>
       </c>
+      <c r="M13" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>153670</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1052,6 +1175,15 @@
       <c r="L14" t="n">
         <v>1.43</v>
       </c>
+      <c r="M14" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>221113</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1096,6 +1228,15 @@
       <c r="L15" t="n">
         <v>0.4</v>
       </c>
+      <c r="M15" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16536</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1140,6 +1281,15 @@
       <c r="L16" t="n">
         <v>0.02</v>
       </c>
+      <c r="M16" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>28011</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1184,6 +1334,15 @@
       <c r="L17" t="n">
         <v>0.33</v>
       </c>
+      <c r="M17" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>141858</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1227,6 +1386,15 @@
       </c>
       <c r="L18" t="n">
         <v>0.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>18590</v>
       </c>
     </row>
   </sheetData>
@@ -1240,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1472,21 @@
           <t>fcf_yield</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1348,6 +1531,15 @@
       <c r="L2" t="n">
         <v>0.63</v>
       </c>
+      <c r="M2" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>98692</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1391,6 +1583,15 @@
       </c>
       <c r="L3" t="n">
         <v>-0.27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>139078</v>
       </c>
     </row>
   </sheetData>
@@ -1404,7 +1605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1669,21 @@
           <t>fcf_yield</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1512,6 +1728,15 @@
       <c r="L2" t="n">
         <v>0.91</v>
       </c>
+      <c r="M2" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>68904</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1556,6 +1781,15 @@
       <c r="L3" t="n">
         <v>0.15</v>
       </c>
+      <c r="M3" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12375</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1600,6 +1834,15 @@
       <c r="L4" t="n">
         <v>-4.5</v>
       </c>
+      <c r="M4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>96421</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1644,6 +1887,15 @@
       <c r="L5" t="n">
         <v>0.05</v>
       </c>
+      <c r="M5" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4270</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1687,6 +1939,15 @@
       </c>
       <c r="L6" t="n">
         <v>0.13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>35517</v>
       </c>
     </row>
     <row r="7">
@@ -1730,6 +1991,15 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4475</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1774,6 +2044,15 @@
       <c r="L8" t="n">
         <v>0.01</v>
       </c>
+      <c r="M8" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>50789</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1818,6 +2097,15 @@
       <c r="L9" t="n">
         <v>0.01</v>
       </c>
+      <c r="M9" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15206</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1861,6 +2149,15 @@
       </c>
       <c r="L10" t="n">
         <v>0.08</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>51084</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1938,6 +2235,21 @@
           <t>fcf_yield</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1982,6 +2294,15 @@
       <c r="L2" t="n">
         <v>0.13</v>
       </c>
+      <c r="M2" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>35517</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2026,6 +2347,15 @@
       <c r="L3" t="n">
         <v>0.4</v>
       </c>
+      <c r="M3" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16536</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2069,6 +2399,15 @@
       </c>
       <c r="L4" t="n">
         <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>142324</v>
       </c>
     </row>
     <row r="5">
@@ -2112,6 +2451,15 @@
       <c r="L5" t="n">
         <v>0.31</v>
       </c>
+      <c r="M5" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>283649</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2156,6 +2504,15 @@
       <c r="L6" t="n">
         <v>0.91</v>
       </c>
+      <c r="M6" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>68904</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2200,6 +2557,15 @@
       <c r="L7" t="n">
         <v>0.04</v>
       </c>
+      <c r="M7" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16727</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2244,6 +2610,15 @@
       <c r="L8" t="n">
         <v>10.45</v>
       </c>
+      <c r="M8" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>899041</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2287,6 +2662,15 @@
       </c>
       <c r="L9" t="n">
         <v>0.85</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>48497</v>
       </c>
     </row>
     <row r="10">
@@ -2328,6 +2712,13 @@
       <c r="L10" t="n">
         <v>0.18</v>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>24394</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2370,6 +2761,15 @@
       <c r="L11" t="n">
         <v>2.68</v>
       </c>
+      <c r="M11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>110519</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2412,6 +2812,15 @@
       <c r="L12" t="n">
         <v>0.46</v>
       </c>
+      <c r="M12" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>845966</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2454,6 +2863,15 @@
       <c r="L13" t="n">
         <v>3</v>
       </c>
+      <c r="M13" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>437928</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2498,6 +2916,15 @@
       <c r="L14" t="n">
         <v>0.99</v>
       </c>
+      <c r="M14" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>44870</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2541,6 +2968,15 @@
       </c>
       <c r="L15" t="n">
         <v>0.15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12375</v>
       </c>
     </row>
     <row r="16">
@@ -2584,6 +3020,15 @@
       <c r="L16" t="n">
         <v>0.04</v>
       </c>
+      <c r="M16" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>20487</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2626,6 +3071,15 @@
       <c r="L17" t="n">
         <v>0.95</v>
       </c>
+      <c r="M17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>159516</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2669,6 +3123,15 @@
       </c>
       <c r="L18" t="n">
         <v>1.84</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12404</v>
       </c>
     </row>
     <row r="19">
@@ -2712,6 +3175,15 @@
       <c r="L19" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="M19" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1702</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2756,6 +3228,15 @@
       <c r="L20" t="n">
         <v>0.02</v>
       </c>
+      <c r="M20" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19059</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2800,6 +3281,15 @@
       <c r="L21" t="n">
         <v>0.06</v>
       </c>
+      <c r="M21" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20521</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2844,6 +3334,15 @@
       <c r="L22" t="n">
         <v>0.08</v>
       </c>
+      <c r="M22" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>51084</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2887,6 +3386,15 @@
       </c>
       <c r="L23" t="n">
         <v>6.49</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>45843</v>
       </c>
     </row>
     <row r="24">
@@ -2930,6 +3438,15 @@
       <c r="L24" t="n">
         <v>0.3</v>
       </c>
+      <c r="M24" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>26645</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2974,6 +3491,15 @@
       <c r="L25" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="M25" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>30381</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3018,6 +3544,15 @@
       <c r="L26" t="n">
         <v>0.01</v>
       </c>
+      <c r="M26" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>18590</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3062,6 +3597,15 @@
       <c r="L27" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="M27" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6427</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3106,6 +3650,15 @@
       <c r="L28" t="n">
         <v>0.17</v>
       </c>
+      <c r="M28" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>35495</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3149,6 +3702,15 @@
       </c>
       <c r="L29" t="n">
         <v>0.63</v>
+      </c>
+      <c r="M29" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>98692</v>
       </c>
     </row>
   </sheetData>
@@ -3162,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3225,6 +3787,180 @@
         <is>
           <t>fcf_yield</t>
         </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ITC Ltd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15616</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="K2" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>70866</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bosch Ltd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>970</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16727</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>141858</v>
       </c>
     </row>
   </sheetData>
@@ -3238,7 +3974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3302,6 +4038,21 @@
           <t>fcf_yield</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sales_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>de_declining</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3346,6 +4097,15 @@
       <c r="L2" t="n">
         <v>0.05</v>
       </c>
+      <c r="M2" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3390,146 +4150,184 @@
       <c r="L3" t="n">
         <v>0.15</v>
       </c>
+      <c r="M3" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12375</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Interglobe Aviation Ltd</t>
+          <t>Indian Oil Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>892.5700000000001</v>
+        <v>23.53</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>9424</v>
+        <v>39635</v>
       </c>
       <c r="G4" t="n">
-        <v>76.23</v>
+        <v>28.61</v>
       </c>
       <c r="H4" t="n">
-        <v>4.27</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>19.31</v>
+        <v>8.01</v>
       </c>
       <c r="J4" t="n">
-        <v>120.69</v>
+        <v>20.1</v>
       </c>
       <c r="K4" t="n">
-        <v>89.68000000000001</v>
+        <v>43.44</v>
       </c>
       <c r="L4" t="n">
-        <v>0.91</v>
+        <v>2.79</v>
+      </c>
+      <c r="M4" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>776352</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd</t>
+          <t>Adani Ports &amp; Special Economic Zone Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>15.35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="F5" t="n">
-        <v>1469</v>
+        <v>8250</v>
       </c>
       <c r="G5" t="n">
-        <v>37.73</v>
+        <v>48.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.37</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>31.61</v>
+        <v>19.58</v>
       </c>
       <c r="J5" t="n">
-        <v>19.3</v>
+        <v>14.91</v>
       </c>
       <c r="K5" t="n">
-        <v>59.23</v>
+        <v>66.37</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>26711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.9</v>
+        <v>13.56</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="F6" t="n">
-        <v>1752</v>
+        <v>278</v>
       </c>
       <c r="G6" t="n">
-        <v>64.52</v>
+        <v>72.53</v>
       </c>
       <c r="H6" t="n">
-        <v>4.43</v>
+        <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>30.33</v>
+        <v>20.48</v>
       </c>
       <c r="J6" t="n">
-        <v>24.78</v>
+        <v>22.97</v>
       </c>
       <c r="K6" t="n">
-        <v>69.84</v>
+        <v>48.98</v>
       </c>
       <c r="L6" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>50789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Titan Company Ltd</t>
+          <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3538,42 +4336,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37.22</v>
+        <v>15.75</v>
       </c>
       <c r="E7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1506</v>
+        <v>4936</v>
       </c>
       <c r="G7" t="n">
-        <v>10.13</v>
+        <v>20.78</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="I7" t="n">
-        <v>20.9</v>
+        <v>10.51</v>
       </c>
       <c r="J7" t="n">
-        <v>20.27</v>
+        <v>12.01</v>
       </c>
       <c r="K7" t="n">
-        <v>67.16</v>
+        <v>48.58</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>141858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd</t>
+          <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3582,84 +4389,104 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.86</v>
+        <v>35.51</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28</v>
+        <v>0.72</v>
       </c>
       <c r="F8" t="n">
-        <v>4360</v>
+        <v>25415</v>
       </c>
       <c r="G8" t="n">
-        <v>25.84</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31</v>
+        <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>11.83</v>
+        <v>8.48</v>
       </c>
       <c r="J8" t="n">
-        <v>8.609999999999999</v>
+        <v>25.79</v>
       </c>
       <c r="K8" t="n">
-        <v>46.19</v>
+        <v>51.97</v>
       </c>
       <c r="L8" t="n">
-        <v>0.28</v>
+        <v>5.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>448083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd</t>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>16.94</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.45</v>
+      </c>
       <c r="F9" t="n">
-        <v>2469</v>
+        <v>42060</v>
       </c>
       <c r="G9" t="n">
-        <v>49.42</v>
+        <v>18.15</v>
       </c>
       <c r="H9" t="n">
-        <v>4.33</v>
+        <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>21.95</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>23.87</v>
+        <v>10.97</v>
       </c>
       <c r="K9" t="n">
-        <v>38.64</v>
+        <v>45.89</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31</v>
+        <v>10.78</v>
+      </c>
+      <c r="M9" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>591396</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation</t>
+          <t>Reliance Industries Ltd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3668,130 +4495,155 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.53</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="F10" t="n">
-        <v>39635</v>
+        <v>45207</v>
       </c>
       <c r="G10" t="n">
-        <v>28.61</v>
+        <v>58.34</v>
       </c>
       <c r="H10" t="n">
-        <v>1.25</v>
+        <v>4.21</v>
       </c>
       <c r="I10" t="n">
-        <v>8.01</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>20.1</v>
+        <v>14.68</v>
       </c>
       <c r="K10" t="n">
-        <v>43.44</v>
+        <v>37.32</v>
       </c>
       <c r="L10" t="n">
-        <v>2.79</v>
+        <v>10.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>899041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adani Ports &amp; Special Economic Zone Ltd</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.35</v>
+        <v>48.28</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>8250</v>
+        <v>10689</v>
       </c>
       <c r="G11" t="n">
-        <v>48.9</v>
+        <v>44.57</v>
       </c>
       <c r="H11" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="I11" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14.91</v>
-      </c>
+        <v>16.09</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>66.37</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>0.78</v>
+      </c>
+      <c r="M11" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>50351</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd</t>
+          <t>Tata Power Company Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.56</v>
+        <v>13.23</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03</v>
+        <v>1.66</v>
       </c>
       <c r="F12" t="n">
-        <v>278</v>
+        <v>3569</v>
       </c>
       <c r="G12" t="n">
-        <v>72.53</v>
+        <v>14.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>0.49</v>
       </c>
       <c r="I12" t="n">
-        <v>20.48</v>
+        <v>15.51</v>
       </c>
       <c r="J12" t="n">
-        <v>22.97</v>
+        <v>10.43</v>
       </c>
       <c r="K12" t="n">
-        <v>48.98</v>
+        <v>35.78</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
+      </c>
+      <c r="M12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>61449</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd</t>
+          <t>Tata Motors Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3800,174 +4652,208 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.75</v>
+        <v>37.46</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="F13" t="n">
-        <v>4936</v>
+        <v>45133</v>
       </c>
       <c r="G13" t="n">
-        <v>20.78</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12.01</v>
-      </c>
+        <v>7.72</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>48.58</v>
+        <v>41.56</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>437928</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd</t>
+          <t>Bosch Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35.51</v>
+        <v>20.64</v>
       </c>
       <c r="E14" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>25415</v>
+        <v>970</v>
       </c>
       <c r="G14" t="n">
-        <v>68.15000000000001</v>
+        <v>58.43</v>
       </c>
       <c r="H14" t="n">
-        <v>1.15</v>
+        <v>4.23</v>
       </c>
       <c r="I14" t="n">
-        <v>8.48</v>
+        <v>6.72</v>
       </c>
       <c r="J14" t="n">
-        <v>25.79</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>51.97</v>
+        <v>44.68</v>
       </c>
       <c r="L14" t="n">
-        <v>5.42</v>
+        <v>0.04</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>16727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corpn Ltd</t>
+          <t>Pidilite Industries Ltd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.94</v>
+        <v>20.78</v>
       </c>
       <c r="E15" t="n">
-        <v>0.45</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>42060</v>
+        <v>955</v>
       </c>
       <c r="G15" t="n">
-        <v>18.15</v>
+        <v>36.12</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>11.84</v>
       </c>
       <c r="J15" t="n">
-        <v>10.97</v>
+        <v>13.49</v>
       </c>
       <c r="K15" t="n">
-        <v>45.89</v>
+        <v>62.19</v>
       </c>
       <c r="L15" t="n">
-        <v>10.78</v>
+        <v>0.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12383</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd</t>
+          <t>Hindalco Industries Ltd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.960000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E16" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="F16" t="n">
-        <v>45207</v>
+        <v>9789</v>
       </c>
       <c r="G16" t="n">
-        <v>58.34</v>
+        <v>56.45</v>
       </c>
       <c r="H16" t="n">
-        <v>4.21</v>
+        <v>0.98</v>
       </c>
       <c r="I16" t="n">
-        <v>9.609999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="J16" t="n">
-        <v>14.68</v>
+        <v>13.07</v>
       </c>
       <c r="K16" t="n">
-        <v>37.32</v>
+        <v>41.64</v>
       </c>
       <c r="L16" t="n">
-        <v>10.45</v>
+        <v>1.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>215962</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adani Power Ltd</t>
+          <t>NTPC Ltd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3976,1507 +4862,517 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48.28</v>
+        <v>13.27</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>1.48</v>
       </c>
       <c r="F17" t="n">
-        <v>10689</v>
+        <v>8644</v>
       </c>
       <c r="G17" t="n">
-        <v>44.57</v>
+        <v>30.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.65</v>
+        <v>0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>12.22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8.74</v>
+      </c>
       <c r="K17" t="n">
-        <v>71.45999999999999</v>
+        <v>36.31</v>
       </c>
       <c r="L17" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>178501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
+          <t>Infosys Ltd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22.17</v>
+        <v>29.79</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>890</v>
+        <v>20117</v>
       </c>
       <c r="G18" t="n">
-        <v>15.62</v>
+        <v>35.99</v>
       </c>
       <c r="H18" t="n">
-        <v>4.41</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>11.04</v>
+        <v>13.2</v>
       </c>
       <c r="J18" t="n">
-        <v>12.68</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>53.22</v>
+        <v>59.85</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>1.81</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>153670</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Power Company Ltd</t>
+          <t>Shree Cement Ltd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.23</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.66</v>
+        <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>3569</v>
+        <v>1929</v>
       </c>
       <c r="G19" t="n">
-        <v>14.5</v>
+        <v>25.87</v>
       </c>
       <c r="H19" t="n">
-        <v>0.49</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>15.51</v>
+        <v>10.33</v>
       </c>
       <c r="J19" t="n">
-        <v>10.43</v>
+        <v>11.29</v>
       </c>
       <c r="K19" t="n">
-        <v>35.78</v>
+        <v>43.17</v>
       </c>
       <c r="L19" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20521</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Chain of Indian private hospitals</t>
+          <t>Bharti Airtel Ltd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.48</v>
+        <v>10.36</v>
       </c>
       <c r="E20" t="n">
-        <v>0.77</v>
+        <v>2.61</v>
       </c>
       <c r="F20" t="n">
-        <v>383</v>
+        <v>27809</v>
       </c>
       <c r="G20" t="n">
-        <v>47.72</v>
+        <v>63.78</v>
       </c>
       <c r="H20" t="n">
-        <v>3.22</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>14.66</v>
+        <v>13.17</v>
       </c>
       <c r="J20" t="n">
-        <v>36.13</v>
+        <v>38.36</v>
       </c>
       <c r="K20" t="n">
-        <v>52.82</v>
+        <v>38.26</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02</v>
+        <v>7.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>149982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd</t>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>15.09</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.05</v>
+      </c>
       <c r="F21" t="n">
-        <v>12547</v>
+        <v>11372</v>
       </c>
       <c r="G21" t="n">
-        <v>25.76</v>
+        <v>37.9</v>
       </c>
       <c r="H21" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="I21" t="n">
-        <v>17.25</v>
+        <v>10.78</v>
       </c>
       <c r="J21" t="n">
-        <v>51.95</v>
+        <v>24.54</v>
       </c>
       <c r="K21" t="n">
-        <v>47.33</v>
+        <v>63.91</v>
       </c>
       <c r="L21" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>48497</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Havells India Ltd</t>
+          <t>ITC Ltd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.07</v>
+        <v>27.85</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>335</v>
+        <v>15616</v>
       </c>
       <c r="G22" t="n">
-        <v>45.41</v>
+        <v>47.85</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6</v>
+        <v>4.26</v>
       </c>
       <c r="I22" t="n">
-        <v>13.04</v>
+        <v>7.95</v>
       </c>
       <c r="J22" t="n">
-        <v>10.03</v>
+        <v>10.08</v>
       </c>
       <c r="K22" t="n">
-        <v>45.41</v>
+        <v>65.44</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>4.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>70866</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd</t>
+          <t>Tech Mahindra Ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>37.46</v>
+        <v>8.99</v>
       </c>
       <c r="E23" t="n">
-        <v>1.26</v>
+        <v>0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>45133</v>
+        <v>5058</v>
       </c>
       <c r="G23" t="n">
-        <v>67.06999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>0.64</v>
       </c>
       <c r="I23" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-10.99</v>
+      </c>
       <c r="K23" t="n">
-        <v>41.56</v>
+        <v>42.99</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>0.17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>51996</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bosch Ltd</t>
+          <t>Abbott India Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20.64</v>
+        <v>32.47</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F24" t="n">
-        <v>970</v>
+        <v>5622</v>
       </c>
       <c r="G24" t="n">
-        <v>58.43</v>
+        <v>75.58</v>
       </c>
       <c r="H24" t="n">
-        <v>4.23</v>
+        <v>0.96</v>
       </c>
       <c r="I24" t="n">
-        <v>6.72</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>9.279999999999999</v>
+        <v>21.69</v>
       </c>
       <c r="K24" t="n">
-        <v>44.68</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04</v>
+        <v>0.37</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5849</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Cipla Ltd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.55</v>
+        <v>15.55</v>
       </c>
       <c r="E25" t="n">
-        <v>0.76</v>
+        <v>0.02</v>
       </c>
       <c r="F25" t="n">
-        <v>925</v>
+        <v>1152</v>
       </c>
       <c r="G25" t="n">
-        <v>9.539999999999999</v>
+        <v>59.75</v>
       </c>
       <c r="H25" t="n">
-        <v>2.18</v>
+        <v>0.12</v>
       </c>
       <c r="I25" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="J25" t="n">
-        <v>7.56</v>
+        <v>22.73</v>
       </c>
       <c r="K25" t="n">
-        <v>32.73</v>
+        <v>62.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>25774</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd</t>
+          <t>Torrent Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
+        <v>24.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.59</v>
+      </c>
       <c r="F26" t="n">
-        <v>6766</v>
+        <v>3106</v>
       </c>
       <c r="G26" t="n">
-        <v>32.9</v>
+        <v>46.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="I26" t="n">
-        <v>13.52</v>
+        <v>6.93</v>
       </c>
       <c r="J26" t="n">
-        <v>20.38</v>
+        <v>30.59</v>
       </c>
       <c r="K26" t="n">
-        <v>37.21</v>
+        <v>58.92</v>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Pidilite Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F27" t="n">
-        <v>955</v>
-      </c>
-      <c r="G27" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I27" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="J27" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="K27" t="n">
-        <v>62.19</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Indian Railway Finance Corporation Ltd</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>7906</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I28" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="J28" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="K28" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>486</v>
-      </c>
-      <c r="G29" t="n">
-        <v>49</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I29" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="J29" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="K29" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Adani Energy Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1095</v>
-      </c>
-      <c r="G30" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I30" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="J30" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="K30" t="n">
-        <v>34.69</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Hindalco Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9789</v>
-      </c>
-      <c r="G31" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="J31" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="K31" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Asian Paints Indian Multi-National Paint and Coating Manufacturing Company</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3556</v>
-      </c>
-      <c r="G32" t="n">
-        <v>73.37</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I32" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="K32" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L32" t="n">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Larsen &amp; Toubro Ltd</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>77.67</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>16087</v>
-      </c>
-      <c r="G33" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I33" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="J33" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="K33" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bajaj Auto Ltd</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6486</v>
-      </c>
-      <c r="G34" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="I34" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="K34" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NTPC Ltd</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8644</v>
-      </c>
-      <c r="G35" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I35" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="J35" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="K35" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Coal India Ltd</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>45.17</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F36" t="n">
-        <v>13617</v>
-      </c>
-      <c r="G36" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="K36" t="n">
-        <v>69.94</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>State Bank of India</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>21632</v>
-      </c>
-      <c r="G37" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I37" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="J37" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="K37" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Canara Bank</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>13296</v>
-      </c>
-      <c r="G38" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="I38" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="J38" t="n">
-        <v>85.78</v>
-      </c>
-      <c r="K38" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Infosys Ltd</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>29.79</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F39" t="n">
-        <v>20117</v>
-      </c>
-      <c r="G39" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J39" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="K39" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SHREECEM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Shree Cement Ltd</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1929</v>
-      </c>
-      <c r="G40" t="n">
-        <v>25.87</v>
-      </c>
-      <c r="H40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="J40" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="K40" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Bharti Airtel Ltd</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="F41" t="n">
-        <v>27809</v>
-      </c>
-      <c r="G41" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I41" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="J41" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="K41" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="L41" t="n">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Dr Reddys Laboratories Ltd</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>19.74</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F42" t="n">
-        <v>509</v>
-      </c>
-      <c r="G42" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I42" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="J42" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="K42" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services Ltd</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F43" t="n">
-        <v>38247</v>
-      </c>
-      <c r="G43" t="n">
-        <v>78.69</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I43" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="K43" t="n">
-        <v>67.95999999999999</v>
-      </c>
-      <c r="L43" t="n">
-        <v>8.289999999999999</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Tata Steel Ltd</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>-5.33</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F44" t="n">
-        <v>6048</v>
-      </c>
-      <c r="G44" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="M26" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="N26" t="b">
         <v>1</v>
       </c>
-      <c r="I44" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>HCL Technologies Ltd</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F45" t="n">
-        <v>15840</v>
-      </c>
-      <c r="G45" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I45" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="J45" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="K45" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F46" t="n">
-        <v>11372</v>
-      </c>
-      <c r="G46" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I46" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="J46" t="n">
-        <v>24.54</v>
-      </c>
-      <c r="K46" t="n">
-        <v>63.91</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ITC Ltd</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>27.85</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>15616</v>
-      </c>
-      <c r="G47" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="J47" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="K47" t="n">
-        <v>65.44</v>
-      </c>
-      <c r="L47" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Tech Mahindra Ltd</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5058</v>
-      </c>
-      <c r="G48" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-10.99</v>
-      </c>
-      <c r="K48" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Abbott India Ltd</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F49" t="n">
-        <v>5622</v>
-      </c>
-      <c r="G49" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I49" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="J49" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="K49" t="n">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CIPLA</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Cipla Ltd</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>15.55</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1152</v>
-      </c>
-      <c r="G50" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I50" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J50" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="K50" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Torrent Pharmaceuticals Ltd</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3106</v>
-      </c>
-      <c r="G51" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="J51" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="K51" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.17</v>
+      <c r="O26" t="n">
+        <v>10728</v>
       </c>
     </row>
   </sheetData>

--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Value Pick" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Growth Accelerator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dividend Champion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt Free Blue Chip" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Debt-Free Blue Chip" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Turnaround Watch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +30,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,8 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,83 +439,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
@@ -514,251 +594,358 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>892.5700000000001</v>
       </c>
       <c r="E2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>11759</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21183</v>
+      </c>
+      <c r="L2" t="n">
+        <v>212</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="R2" t="n">
+        <v>121.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
         <v>76.23</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="J2" t="n">
-        <v>120.69</v>
-      </c>
-      <c r="K2" t="n">
-        <v>89.68000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M2" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>68904</v>
+      <c r="V2" t="n">
+        <v>7.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>34.4</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>50.94</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F3" t="n">
-        <v>667</v>
+        <v>19.14</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.09</v>
       </c>
       <c r="G3" t="n">
-        <v>60.44</v>
+        <v>80.69</v>
       </c>
       <c r="H3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17.96</v>
+        <v>1.66</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>38247</v>
       </c>
       <c r="J3" t="n">
-        <v>29.17</v>
+        <v>6091</v>
       </c>
       <c r="K3" t="n">
-        <v>84.78</v>
+        <v>44338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05</v>
+        <v>127</v>
       </c>
       <c r="M3" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>58</v>
       </c>
       <c r="O3" t="n">
-        <v>4270</v>
+        <v>1.62</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="S3" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adani Power Ltd</t>
+          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>48.28</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>34.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10689</v>
+        <v>26.02</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.02</v>
       </c>
       <c r="G4" t="n">
-        <v>44.57</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I4" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>215</v>
+      </c>
       <c r="K4" t="n">
-        <v>71.45999999999999</v>
+        <v>882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.78</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
+        <v>2.02</v>
+      </c>
+      <c r="N4" t="n">
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>50351</v>
+        <v>1.08</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="S4" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="U4" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>22.9</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>48.28</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1752</v>
+        <v>41.37</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>64.52</v>
+        <v>7.14</v>
       </c>
       <c r="H5" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30.33</v>
+        <v>0.55</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>10689</v>
       </c>
       <c r="J5" t="n">
-        <v>24.78</v>
+        <v>3481</v>
       </c>
       <c r="K5" t="n">
-        <v>69.84</v>
+        <v>14170</v>
       </c>
       <c r="L5" t="n">
-        <v>0.13</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="N5" t="b">
+        <v>1.12</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>35517</v>
+        <v>1.65</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="R5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="T5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd</t>
+          <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>50.94</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>77.67</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F6" t="n">
-        <v>38247</v>
+        <v>7.03</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>78.69</v>
+        <v>3.16</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.46</v>
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>16087</v>
       </c>
       <c r="J6" t="n">
-        <v>7.87</v>
+        <v>2179</v>
       </c>
       <c r="K6" t="n">
-        <v>67.95999999999999</v>
+        <v>18266</v>
       </c>
       <c r="L6" t="n">
-        <v>8.289999999999999</v>
+        <v>95</v>
       </c>
       <c r="M6" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
+        <v>66.73</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
       </c>
       <c r="O6" t="n">
-        <v>240893</v>
+        <v>1.26</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="S6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.48</v>
       </c>
     </row>
     <row r="7">
@@ -777,370 +964,517 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>36.31</v>
       </c>
       <c r="E7" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>508</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L7" t="n">
+        <v>42</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="S7" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="U7" t="n">
         <v>8.65</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I7" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="J7" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>12375</v>
+      <c r="V7" t="n">
+        <v>11.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Asian Paints Indian Multi-National Paint and Coating Manufacturing Company</t>
+          <t>Infosys Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>29.68</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>29.79</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3556</v>
+        <v>17.08</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.09</v>
       </c>
       <c r="G8" t="n">
-        <v>73.37</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I8" t="n">
-        <v>13.03</v>
+        <v>1.13</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>20117</v>
       </c>
       <c r="J8" t="n">
-        <v>20.28</v>
+        <v>5093</v>
       </c>
       <c r="K8" t="n">
-        <v>66.59999999999999</v>
+        <v>25210</v>
       </c>
       <c r="L8" t="n">
-        <v>0.17</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
+        <v>4.25</v>
+      </c>
+      <c r="N8" t="n">
+        <v/>
       </c>
       <c r="O8" t="n">
-        <v>35495</v>
+        <v>4.1</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="R8" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="S8" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="U8" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adani Ports &amp; Special Economic Zone Ltd</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>15.35</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>22.9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8250</v>
+        <v>12.91</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>48.9</v>
+        <v>28.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I9" t="n">
-        <v>19.58</v>
+        <v>1.29</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1752</v>
       </c>
       <c r="J9" t="n">
-        <v>14.91</v>
+        <v>3918</v>
       </c>
       <c r="K9" t="n">
-        <v>66.37</v>
+        <v>5670</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>155</v>
       </c>
       <c r="M9" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="N9" t="b">
-        <v>1</v>
+        <v>66.73</v>
+      </c>
+      <c r="N9" t="n">
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>26711</v>
+        <v>4.43</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="U9" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
+          <t>Asian Paints Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>15.09</v>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>29.68</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11372</v>
+        <v>15.66</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>37.9</v>
+        <v>36.84</v>
       </c>
       <c r="H10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.78</v>
+        <v>1.19</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>3556</v>
       </c>
       <c r="J10" t="n">
-        <v>24.54</v>
+        <v>2548</v>
       </c>
       <c r="K10" t="n">
-        <v>63.91</v>
+        <v>6104</v>
       </c>
       <c r="L10" t="n">
-        <v>0.85</v>
+        <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
+        <v>19.51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>58</v>
       </c>
       <c r="O10" t="n">
-        <v>48497</v>
+        <v>2.42</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="R10" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="S10" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>20.78</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>23.01</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F11" t="n">
-        <v>955</v>
+        <v>14.29</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.08</v>
       </c>
       <c r="G11" t="n">
-        <v>36.12</v>
+        <v>38.92</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.84</v>
+        <v>1.11</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15840</v>
       </c>
       <c r="J11" t="n">
-        <v>13.49</v>
+        <v>6608</v>
       </c>
       <c r="K11" t="n">
-        <v>62.19</v>
+        <v>22448</v>
       </c>
       <c r="L11" t="n">
-        <v>0.59</v>
+        <v>58</v>
       </c>
       <c r="M11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N11" t="b">
-        <v>1</v>
+        <v>12.57</v>
+      </c>
+      <c r="N11" t="n">
+        <v>90</v>
       </c>
       <c r="O11" t="n">
-        <v>12383</v>
+        <v>1.99</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="S11" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="T11" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="U11" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd</t>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>23.01</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>15.09</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F12" t="n">
-        <v>15840</v>
+        <v>19.82</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="G12" t="n">
-        <v>63.63</v>
+        <v>47.59</v>
       </c>
       <c r="H12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12.71</v>
+        <v>0.57</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>11372</v>
       </c>
       <c r="J12" t="n">
-        <v>9.19</v>
+        <v>763</v>
       </c>
       <c r="K12" t="n">
-        <v>62.04</v>
+        <v>12135</v>
       </c>
       <c r="L12" t="n">
-        <v>3.84</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
+        <v>26.53</v>
+      </c>
+      <c r="N12" t="n">
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>109913</v>
+        <v>3.88</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="R12" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infosys Ltd</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>29.79</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>22.17</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20117</v>
+        <v>24.2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>35.99</v>
+        <v>103</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>13.2</v>
+        <v>0.72</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>890</v>
       </c>
       <c r="J13" t="n">
-        <v>11.24</v>
+        <v>2834</v>
       </c>
       <c r="K13" t="n">
-        <v>59.85</v>
+        <v>3724</v>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>146</v>
       </c>
       <c r="M13" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
+        <v>66.83</v>
+      </c>
+      <c r="N13" t="n">
+        <v>35</v>
       </c>
       <c r="O13" t="n">
-        <v>153670</v>
+        <v>4.41</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="S13" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="T13" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="U13" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
+          <t>Adani Ports &amp; Special Economic Zone Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1148,147 +1482,210 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>77.67</v>
+      <c r="D14" s="2" t="n">
+        <v>15.35</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16087</v>
+        <v>30.34</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>30.8</v>
+        <v>4.53</v>
       </c>
       <c r="H14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10.34</v>
+        <v>0.23</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>8250</v>
       </c>
       <c r="J14" t="n">
-        <v>8.76</v>
+        <v>6768</v>
       </c>
       <c r="K14" t="n">
-        <v>57.41</v>
+        <v>15018</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>38</v>
       </c>
       <c r="M14" t="n">
-        <v>17.59</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
+        <v>12.22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16</v>
       </c>
       <c r="O14" t="n">
-        <v>221113</v>
+        <v>1.16</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="S14" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="T14" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="U14" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
+          <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>22.17</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>19.74</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F15" t="n">
-        <v>890</v>
+        <v>19.91</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>15.62</v>
+        <v>43.11</v>
       </c>
       <c r="H15" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.04</v>
+        <v>0.72</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>509</v>
       </c>
       <c r="J15" t="n">
-        <v>12.68</v>
+        <v>4034</v>
       </c>
       <c r="K15" t="n">
-        <v>53.22</v>
+        <v>4543</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>23.78</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
+        <v>34.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>16536</v>
+        <v>0.09</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="R15" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="S15" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>10.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd</t>
+          <t>Pidilite Industries Ltd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>19.74</v>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>20.78</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>509</v>
+        <v>14.11</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="G16" t="n">
-        <v>11.73</v>
+        <v>47.65</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I16" t="n">
-        <v>12.64</v>
+        <v>1.03</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>955</v>
       </c>
       <c r="J16" t="n">
-        <v>23.39</v>
+        <v>1769</v>
       </c>
       <c r="K16" t="n">
-        <v>52.36</v>
+        <v>2724</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02</v>
+        <v>34</v>
       </c>
       <c r="M16" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
+        <v>16.48</v>
+      </c>
+      <c r="N16" t="n">
+        <v>47</v>
       </c>
       <c r="O16" t="n">
-        <v>28011</v>
+        <v>1.01</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R16" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="S16" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="V16" t="n">
+        <v>12.3</v>
       </c>
     </row>
     <row r="17">
@@ -1307,41 +1704,62 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>15.75</v>
       </c>
       <c r="E17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>11865</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16801</v>
+      </c>
+      <c r="L17" t="n">
+        <v>429</v>
+      </c>
+      <c r="M17" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="N17" t="n">
+        <v>29</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="S17" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="T17" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="U17" t="n">
         <v>20.78</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="K17" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>141858</v>
+      <c r="V17" t="n">
+        <v>8.26</v>
       </c>
     </row>
     <row r="18">
@@ -1360,41 +1778,62 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>17.07</v>
       </c>
       <c r="E18" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>1618</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1953</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="N18" t="n">
+        <v>44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>43</v>
+      </c>
+      <c r="T18" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="U18" t="n">
         <v>45.41</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="K18" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>18590</v>
+      <c r="V18" t="n">
+        <v>14.08</v>
       </c>
     </row>
   </sheetData>
@@ -1408,190 +1847,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Indian Oil Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.55</v>
+        <v>23.53</v>
       </c>
       <c r="E2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F2" t="n">
-        <v>925</v>
+        <v>5.56</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.72</v>
       </c>
       <c r="G2" t="n">
-        <v>9.539999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="H2" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>9.210000000000001</v>
+        <v>39635</v>
       </c>
       <c r="J2" t="n">
-        <v>7.56</v>
+        <v>31464</v>
       </c>
       <c r="K2" t="n">
-        <v>32.73</v>
+        <v>71099</v>
       </c>
       <c r="L2" t="n">
-        <v>0.63</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>98692</v>
+        <v>1.33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>40</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="T2" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson International Ltd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>925</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6644</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7569</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="S3" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Shree Cement Ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1929</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1418</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3347</v>
+      </c>
+      <c r="L4" t="n">
+        <v>480</v>
+      </c>
+      <c r="M4" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="S4" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="T4" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Mahindra &amp; Mahindra Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>18.54</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>1.64</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I5" t="n">
         <v>-11245</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J5" t="n">
+        <v>5615</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5630</v>
+      </c>
+      <c r="L5" t="n">
+        <v>91</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="N5" t="n">
+        <v>21</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>14.22</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="K3" t="n">
-        <v>26.53</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="M3" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>139078</v>
+      <c r="V5" s="2" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1605,83 +2293,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
@@ -1705,37 +2452,58 @@
         <v>892.5700000000001</v>
       </c>
       <c r="E2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="I2" t="n">
         <v>9424</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>11759</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21183</v>
+      </c>
+      <c r="L2" t="n">
+        <v>212</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="R2" t="n">
+        <v>121.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
         <v>76.23</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="J2" t="n">
-        <v>120.69</v>
-      </c>
-      <c r="K2" t="n">
-        <v>89.68000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M2" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>68904</v>
+      <c r="V2" t="n">
+        <v>7.87</v>
       </c>
     </row>
     <row r="3">
@@ -1758,37 +2526,58 @@
         <v>36.31</v>
       </c>
       <c r="E3" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I3" t="n">
         <v>841</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>508</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L3" t="n">
+        <v>42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="S3" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.65</v>
       </c>
-      <c r="H3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I3" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="J3" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M3" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>12375</v>
+      <c r="V3" t="n">
+        <v>11.82</v>
       </c>
     </row>
     <row r="4">
@@ -1811,37 +2600,58 @@
         <v>8.529999999999999</v>
       </c>
       <c r="E4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I4" t="n">
         <v>-8455</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>18767</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10312</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="R4" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="T4" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="U4" t="n">
         <v>58.87</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I4" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="J4" t="n">
-        <v>45.81</v>
-      </c>
-      <c r="K4" t="n">
-        <v>37.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>96421</v>
+      <c r="V4" t="n">
+        <v>10.41</v>
       </c>
     </row>
     <row r="5">
@@ -1864,37 +2674,58 @@
         <v>34.4</v>
       </c>
       <c r="E5" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I5" t="n">
         <v>667</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
+        <v>215</v>
+      </c>
+      <c r="K5" t="n">
+        <v>882</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="R5" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="T5" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="U5" t="n">
         <v>60.44</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="J5" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>84.78</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M5" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4270</v>
+      <c r="V5" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="6">
@@ -1917,37 +2748,58 @@
         <v>22.9</v>
       </c>
       <c r="E6" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I6" t="n">
         <v>1752</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>3918</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5670</v>
+      </c>
+      <c r="L6" t="n">
+        <v>155</v>
+      </c>
+      <c r="M6" t="n">
+        <v>66.73</v>
+      </c>
+      <c r="N6" t="n">
+        <v>42</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="T6" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="U6" t="n">
         <v>64.52</v>
       </c>
-      <c r="H6" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I6" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="J6" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="K6" t="n">
-        <v>69.84</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M6" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>35517</v>
+      <c r="V6" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="7">
@@ -1970,35 +2822,58 @@
         <v>18.66</v>
       </c>
       <c r="E7" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="R7" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="S7" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="U7" t="n">
         <v>56.96</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I7" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="K7" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4475</v>
+      <c r="V7" t="n">
+        <v>5.76</v>
       </c>
     </row>
     <row r="8">
@@ -2021,37 +2896,58 @@
         <v>13.56</v>
       </c>
       <c r="E8" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I8" t="n">
         <v>278</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>2468</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="R8" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="S8" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="U8" t="n">
         <v>72.53</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I8" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="K8" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>50789</v>
+      <c r="V8" t="n">
+        <v>11.71</v>
       </c>
     </row>
     <row r="9">
@@ -2074,37 +2970,58 @@
         <v>7.57</v>
       </c>
       <c r="E9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I9" t="n">
         <v>26</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
+        <v>1911</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1937</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>64</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="S9" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="U9" t="n">
         <v>54.79</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I9" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>15206</v>
+      <c r="V9" t="n">
+        <v>7.14</v>
       </c>
     </row>
     <row r="10">
@@ -2127,37 +3044,58 @@
         <v>37.22</v>
       </c>
       <c r="E10" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I10" t="n">
         <v>1506</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>189</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1695</v>
+      </c>
+      <c r="L10" t="n">
+        <v>39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="N10" t="n">
+        <v>28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="R10" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="T10" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U10" t="n">
         <v>10.13</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="K10" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M10" t="n">
-        <v>33.14</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>51084</v>
+      <c r="V10" t="n">
+        <v>10.51</v>
       </c>
     </row>
   </sheetData>
@@ -2171,83 +3109,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
@@ -2271,37 +3268,58 @@
         <v>22.9</v>
       </c>
       <c r="E2" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>3918</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5670</v>
+      </c>
+      <c r="L2" t="n">
+        <v>155</v>
+      </c>
+      <c r="M2" t="n">
+        <v>66.73</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P2" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="T2" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="U2" t="n">
         <v>64.52</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I2" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="K2" t="n">
-        <v>69.84</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M2" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>35517</v>
+      <c r="V2" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -2324,37 +3342,58 @@
         <v>22.17</v>
       </c>
       <c r="E3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.02</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>103</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>2834</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3724</v>
+      </c>
+      <c r="L3" t="n">
+        <v>146</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P3" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="S3" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="T3" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="U3" t="n">
         <v>15.62</v>
       </c>
-      <c r="H3" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="K3" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>23.78</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>16536</v>
+      <c r="V3" t="n">
+        <v>13.61</v>
       </c>
     </row>
     <row r="4">
@@ -2377,37 +3416,58 @@
         <v>45.17</v>
       </c>
       <c r="E4" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.08</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>13617</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>4486</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18103</v>
+      </c>
+      <c r="L4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="R4" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="S4" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
         <v>34.27</v>
       </c>
-      <c r="H4" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="K4" t="n">
-        <v>69.94</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>142324</v>
+      <c r="V4" t="n">
+        <v>14.75</v>
       </c>
     </row>
     <row r="5">
@@ -2429,36 +3489,59 @@
       <c r="D5" t="n">
         <v>14.34</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>23.07</v>
+      </c>
       <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>2469</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
+        <v>16600</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19069</v>
+      </c>
+      <c r="L5" t="n">
+        <v>84</v>
+      </c>
+      <c r="M5" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="U5" t="n">
         <v>49.42</v>
       </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I5" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="K5" t="n">
-        <v>38.64</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M5" t="n">
-        <v>30.19</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>283649</v>
+      <c r="V5" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="6">
@@ -2481,37 +3564,58 @@
         <v>892.5700000000001</v>
       </c>
       <c r="E6" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.02</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H6" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>11759</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21183</v>
+      </c>
+      <c r="L6" t="n">
+        <v>212</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P6" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="R6" t="n">
+        <v>121.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="n">
         <v>76.23</v>
       </c>
-      <c r="H6" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="J6" t="n">
-        <v>120.69</v>
-      </c>
-      <c r="K6" t="n">
-        <v>89.68000000000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M6" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>68904</v>
+      <c r="V6" t="n">
+        <v>7.87</v>
       </c>
     </row>
     <row r="7">
@@ -2534,37 +3638,58 @@
         <v>20.64</v>
       </c>
       <c r="E7" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>970</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>283</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L7" t="n">
+        <v>844</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="U7" t="n">
         <v>58.43</v>
       </c>
-      <c r="H7" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="K7" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M7" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>16727</v>
+      <c r="V7" t="n">
+        <v>6.47</v>
       </c>
     </row>
     <row r="8">
@@ -2587,37 +3712,58 @@
         <v>9.960000000000001</v>
       </c>
       <c r="E8" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.58</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>45207</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>113581</v>
+      </c>
+      <c r="K8" t="n">
+        <v>158788</v>
+      </c>
+      <c r="L8" t="n">
+        <v>51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="S8" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="T8" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="U8" t="n">
         <v>58.34</v>
       </c>
-      <c r="H8" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="K8" t="n">
-        <v>37.32</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>899041</v>
+      <c r="V8" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="9">
@@ -2640,37 +3786,58 @@
         <v>15.09</v>
       </c>
       <c r="E9" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
+        <v>763</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12135</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="R9" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="S9" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" t="n">
         <v>37.9</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="J9" t="n">
-        <v>24.54</v>
-      </c>
-      <c r="K9" t="n">
-        <v>63.91</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>48497</v>
+      <c r="V9" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="10">
@@ -2693,31 +3860,58 @@
         <v>117.75</v>
       </c>
       <c r="E10" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>1237</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4175</v>
+      </c>
+      <c r="L10" t="n">
+        <v>41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="R10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="T10" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="U10" t="n">
         <v>54.96</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>24394</v>
+      <c r="V10" t="n">
+        <v>14.34</v>
       </c>
     </row>
     <row r="11">
@@ -2739,36 +3933,59 @@
       <c r="D11" t="n">
         <v>16.72</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>13.94</v>
+      </c>
       <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
+        <v>1750</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15046</v>
+      </c>
+      <c r="L11" t="n">
+        <v>17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P11" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="R11" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="U11" t="n">
         <v>36.74</v>
       </c>
-      <c r="H11" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="I11" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="J11" t="n">
-        <v>85.78</v>
-      </c>
-      <c r="K11" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="M11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>110519</v>
+      <c r="V11" t="n">
+        <v>12.61</v>
       </c>
     </row>
     <row r="12">
@@ -2790,36 +4007,59 @@
       <c r="D12" t="n">
         <v>49.45</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4.84</v>
+      </c>
       <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>853</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
+        <v>25269</v>
+      </c>
+      <c r="K12" t="n">
+        <v>26122</v>
+      </c>
+      <c r="L12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="R12" t="n">
+        <v/>
+      </c>
+      <c r="S12" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="T12" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="U12" t="n">
         <v>30.67</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="J12" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="K12" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>845966</v>
+      <c r="V12" t="n">
+        <v>8.1</v>
       </c>
     </row>
     <row r="13">
@@ -2842,35 +4082,58 @@
         <v>37.46</v>
       </c>
       <c r="E13" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.26</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
+        <v>22782</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67915</v>
+      </c>
+      <c r="L13" t="n">
+        <v>94</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v/>
+      </c>
+      <c r="R13" t="n">
+        <v/>
+      </c>
+      <c r="S13" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="T13" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="U13" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>437928</v>
+      <c r="V13" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="14">
@@ -2893,37 +4156,58 @@
         <v>26.61</v>
       </c>
       <c r="E14" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>168.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>6486</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
+        <v>72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6558</v>
+      </c>
+      <c r="L14" t="n">
+        <v>276</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="T14" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="U14" t="n">
         <v>29.91</v>
       </c>
-      <c r="H14" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="M14" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>44870</v>
+      <c r="V14" t="n">
+        <v>9.83</v>
       </c>
     </row>
     <row r="15">
@@ -2946,37 +4230,58 @@
         <v>36.31</v>
       </c>
       <c r="E15" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.43</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
+        <v>508</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L15" t="n">
+        <v>42</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P15" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="S15" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="T15" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="U15" t="n">
         <v>8.65</v>
       </c>
-      <c r="H15" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I15" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="J15" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="K15" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M15" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>12375</v>
+      <c r="V15" t="n">
+        <v>11.82</v>
       </c>
     </row>
     <row r="16">
@@ -2998,36 +4303,59 @@
       <c r="D16" t="n">
         <v>15.72</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>9.369999999999999</v>
+      </c>
       <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
+        <v>1921</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2407</v>
+      </c>
+      <c r="L16" t="n">
+        <v>39</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="S16" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="T16" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="U16" t="n">
         <v>49</v>
       </c>
-      <c r="H16" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I16" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="J16" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="K16" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M16" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>20487</v>
+      <c r="V16" t="n">
+        <v>7.86</v>
       </c>
     </row>
     <row r="17">
@@ -3049,36 +4377,59 @@
       <c r="D17" t="n">
         <v>17.99</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>28.89</v>
+      </c>
       <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>144737</v>
+      </c>
+      <c r="K17" t="n">
+        <v>157284</v>
+      </c>
+      <c r="L17" t="n">
+        <v>63</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="T17" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" t="n">
         <v>25.76</v>
       </c>
-      <c r="H17" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="I17" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="J17" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="K17" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>159516</v>
+      <c r="V17" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="18">
@@ -3101,37 +4452,58 @@
         <v>18.36</v>
       </c>
       <c r="E18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.14</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>1042</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>971</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="S18" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="U18" t="n">
         <v>50.95</v>
       </c>
-      <c r="H18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="I18" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>12404</v>
+      <c r="V18" t="n">
+        <v>13.59</v>
       </c>
     </row>
     <row r="19">
@@ -3153,36 +4525,59 @@
       <c r="D19" t="n">
         <v>13.58</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>432.73</v>
+      </c>
       <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v>3747.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>1469</v>
       </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
+        <v>472</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1941</v>
+      </c>
+      <c r="L19" t="n">
+        <v>653</v>
+      </c>
+      <c r="M19" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="S19" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="T19" t="n">
+        <v>80.04000000000001</v>
+      </c>
+      <c r="U19" t="n">
         <v>37.73</v>
       </c>
-      <c r="H19" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I19" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>59.23</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1702</v>
+      <c r="V19" t="n">
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3205,37 +4600,58 @@
         <v>13.48</v>
       </c>
       <c r="E20" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.77</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>383</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
+        <v>1537</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1920</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="R20" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="S20" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
         <v>47.72</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="I20" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="J20" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>52.82</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M20" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>19059</v>
+      <c r="V20" t="n">
+        <v>7.68</v>
       </c>
     </row>
     <row r="21">
@@ -3258,37 +4674,58 @@
         <v>8.369999999999999</v>
       </c>
       <c r="E21" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.08</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
+        <v>1418</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3347</v>
+      </c>
+      <c r="L21" t="n">
+        <v>480</v>
+      </c>
+      <c r="M21" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="S21" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="T21" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="U21" t="n">
         <v>25.87</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M21" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>20521</v>
+      <c r="V21" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="22">
@@ -3311,37 +4748,58 @@
         <v>37.22</v>
       </c>
       <c r="E22" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.65</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>1506</v>
       </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
+        <v>189</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1695</v>
+      </c>
+      <c r="L22" t="n">
+        <v>39</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="R22" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="S22" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="T22" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U22" t="n">
         <v>10.13</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="K22" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M22" t="n">
-        <v>33.14</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>51084</v>
+      <c r="V22" t="n">
+        <v>10.51</v>
       </c>
     </row>
     <row r="23">
@@ -3364,37 +4822,58 @@
         <v>17.87</v>
       </c>
       <c r="E23" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.42</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>24176</v>
       </c>
-      <c r="G23" t="n">
+      <c r="J23" t="n">
+        <v>13114</v>
+      </c>
+      <c r="K23" t="n">
+        <v>37290</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="T23" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="U23" t="n">
         <v>64.39</v>
       </c>
-      <c r="H23" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="K23" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>45843</v>
+      <c r="V23" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
@@ -3416,36 +4895,59 @@
       <c r="D24" t="n">
         <v>13.04</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>24.06</v>
+      </c>
       <c r="F24" t="n">
+        <v/>
+      </c>
+      <c r="G24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7914</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P24" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="S24" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="T24" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="U24" t="n">
         <v>9.81</v>
       </c>
-      <c r="H24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I24" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="J24" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>26645</v>
+      <c r="V24" t="n">
+        <v>3.91</v>
       </c>
     </row>
     <row r="25">
@@ -3468,37 +4970,58 @@
         <v>3816.58</v>
       </c>
       <c r="E25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" t="n">
         <v>0.62</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
+        <v>238.19</v>
+      </c>
+      <c r="H25" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>1814</v>
       </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
+        <v>6412</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8226</v>
+      </c>
+      <c r="L25" t="n">
+        <v>114</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="R25" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="S25" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="T25" t="n">
+        <v>100</v>
+      </c>
+      <c r="U25" t="n">
         <v>71.89</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="I25" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="K25" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>30381</v>
+      <c r="V25" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="26">
@@ -3521,37 +5044,58 @@
         <v>17.07</v>
       </c>
       <c r="E26" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.04</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
+        <v>1618</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1953</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S26" t="n">
+        <v>43</v>
+      </c>
+      <c r="T26" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="U26" t="n">
         <v>45.41</v>
       </c>
-      <c r="H26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="K26" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>18590</v>
+      <c r="V26" t="n">
+        <v>14.08</v>
       </c>
     </row>
     <row r="27">
@@ -3574,37 +5118,58 @@
         <v>6.91</v>
       </c>
       <c r="E27" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.12</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I27" s="2" t="n">
         <v>1010</v>
       </c>
-      <c r="G27" t="n">
+      <c r="J27" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2539</v>
+      </c>
+      <c r="L27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="S27" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="T27" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" t="n">
         <v>46.26</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-5.14</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>40.34</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6427</v>
+      <c r="V27" t="n">
+        <v>14.32</v>
       </c>
     </row>
     <row r="28">
@@ -3627,37 +5192,58 @@
         <v>29.68</v>
       </c>
       <c r="E28" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.13</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I28" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="G28" t="n">
+      <c r="J28" t="n">
+        <v>2548</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6104</v>
+      </c>
+      <c r="L28" t="n">
+        <v>57</v>
+      </c>
+      <c r="M28" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="R28" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="S28" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="T28" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="U28" t="n">
         <v>73.37</v>
       </c>
-      <c r="H28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I28" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="J28" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="K28" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M28" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>35495</v>
+      <c r="V28" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="29">
@@ -3680,37 +5266,58 @@
         <v>11.55</v>
       </c>
       <c r="E29" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.76</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I29" s="2" t="n">
         <v>925</v>
       </c>
-      <c r="G29" t="n">
+      <c r="J29" t="n">
+        <v>6644</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7569</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="S29" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="T29" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="U29" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="H29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I29" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="K29" t="n">
-        <v>32.73</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="M29" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>98692</v>
+      <c r="V29" t="n">
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>
@@ -3724,243 +5331,1105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ITC Ltd</t>
+          <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>27.85</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>892.5700000000001</v>
       </c>
       <c r="E2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9424</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11759</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21183</v>
+      </c>
+      <c r="L2" t="n">
+        <v>212</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>15616</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="K2" t="n">
-        <v>65.44</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
       <c r="O2" t="n">
-        <v>70866</v>
+        <v>4.27</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="R2" t="n">
+        <v>121.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bosch Ltd</t>
+          <t>Abbott India Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>20.64</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>32.47</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>970</v>
+        <v>20.53</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.02</v>
       </c>
       <c r="G3" t="n">
-        <v>58.43</v>
+        <v>135.83</v>
       </c>
       <c r="H3" t="n">
-        <v>4.23</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>6.72</v>
+        <v>5622</v>
       </c>
       <c r="J3" t="n">
-        <v>9.279999999999999</v>
+        <v>416</v>
       </c>
       <c r="K3" t="n">
-        <v>44.68</v>
+        <v>6038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04</v>
+        <v>565</v>
       </c>
       <c r="M3" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
+        <v>17.61</v>
+      </c>
+      <c r="N3" t="n">
+        <v>73</v>
       </c>
       <c r="O3" t="n">
-        <v>16727</v>
+        <v>0.96</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="R3" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="S3" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="U3" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ITC Ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15616</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1563</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17179</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="N4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>103</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I5" t="n">
+        <v>890</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2834</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3724</v>
+      </c>
+      <c r="L5" t="n">
+        <v>146</v>
+      </c>
+      <c r="M5" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="S5" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="T5" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="U5" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1828</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4923</v>
+      </c>
+      <c r="L6" t="n">
+        <v>187</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S6" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="T6" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="U6" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I7" t="n">
+        <v>955</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1769</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2724</v>
+      </c>
+      <c r="L7" t="n">
+        <v>34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>47</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="S7" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="U7" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bosch Ltd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I8" t="n">
+        <v>970</v>
+      </c>
+      <c r="J8" t="n">
+        <v>283</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L8" t="n">
+        <v>844</v>
+      </c>
+      <c r="M8" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="N8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10145</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5324</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15469</v>
+      </c>
+      <c r="L9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="N9" t="n">
+        <v>96</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>69</v>
+      </c>
+      <c r="U9" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11.88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Havells India Ltd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>335</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1618</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1953</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="N10" t="n">
+        <v>44</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T10" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="U10" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D11" s="2" t="n">
         <v>15.75</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E11" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G11" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I11" t="n">
         <v>4936</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J11" t="n">
+        <v>11865</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16801</v>
+      </c>
+      <c r="L11" t="n">
+        <v>429</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="S11" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="T11" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="U11" t="n">
         <v>20.78</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>141858</v>
+      <c r="V11" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cipla Ltd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1152</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2982</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4134</v>
+      </c>
+      <c r="L12" t="n">
+        <v>51</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="N12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="R12" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="S12" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="T12" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="E13" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11372</v>
+      </c>
+      <c r="J13" t="n">
+        <v>763</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12135</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="N13" t="n">
+        <v>34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="R13" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>278</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2468</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="R14" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="S14" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>11.71</v>
       </c>
     </row>
   </sheetData>
@@ -3974,83 +6443,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asset_turnover</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>capex_cr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>earnings_per_share</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>book_value_per_share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sales_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sales_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf_yield</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sales_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>de_declining</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>sales</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
         </is>
       </c>
     </row>
@@ -4074,37 +6602,58 @@
         <v>34.4</v>
       </c>
       <c r="E2" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.02</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>215</v>
+      </c>
+      <c r="K2" t="n">
+        <v>882</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>47</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="R2" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="S2" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="T2" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="U2" t="n">
         <v>60.44</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>84.78</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M2" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4270</v>
+      <c r="V2" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="3">
@@ -4127,37 +6676,58 @@
         <v>36.31</v>
       </c>
       <c r="E3" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.43</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>508</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L3" t="n">
+        <v>42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="S3" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.65</v>
       </c>
-      <c r="H3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="I3" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="J3" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M3" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>12375</v>
+      <c r="V3" t="n">
+        <v>11.82</v>
       </c>
     </row>
     <row r="4">
@@ -4180,37 +6750,58 @@
         <v>23.53</v>
       </c>
       <c r="E4" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.72</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>39635</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>31464</v>
+      </c>
+      <c r="K4" t="n">
+        <v>71099</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="S4" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="U4" t="n">
         <v>28.61</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="M4" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>776352</v>
+      <c r="V4" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="5">
@@ -4233,37 +6824,58 @@
         <v>15.35</v>
       </c>
       <c r="E5" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>8250</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
+        <v>6768</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15018</v>
+      </c>
+      <c r="L5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="R5" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="S5" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="T5" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="U5" t="n">
         <v>48.9</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="K5" t="n">
-        <v>66.37</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>26711</v>
+      <c r="V5" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="6">
@@ -4286,37 +6898,58 @@
         <v>13.56</v>
       </c>
       <c r="E6" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.03</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>278</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>2468</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L6" t="n">
+        <v>39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P6" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="R6" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="S6" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="T6" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="U6" t="n">
         <v>72.53</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I6" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J6" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="K6" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>50789</v>
+      <c r="V6" t="n">
+        <v>11.71</v>
       </c>
     </row>
     <row r="7">
@@ -4339,37 +6972,58 @@
         <v>15.75</v>
       </c>
       <c r="E7" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>11865</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16801</v>
+      </c>
+      <c r="L7" t="n">
+        <v>429</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="T7" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="U7" t="n">
         <v>20.78</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>141858</v>
+      <c r="V7" t="n">
+        <v>8.26</v>
       </c>
     </row>
     <row r="8">
@@ -4392,37 +7046,58 @@
         <v>35.51</v>
       </c>
       <c r="E8" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.72</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>25415</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>10521</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35936</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N8" t="n">
+        <v>33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="R8" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="S8" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="U8" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="K8" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>448083</v>
+      <c r="V8" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="9">
@@ -4445,37 +7120,58 @@
         <v>16.94</v>
       </c>
       <c r="E9" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.45</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>42060</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
+        <v>57203</v>
+      </c>
+      <c r="K9" t="n">
+        <v>99263</v>
+      </c>
+      <c r="L9" t="n">
+        <v>39</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N9" t="n">
+        <v>31</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="U9" t="n">
         <v>18.15</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="K9" t="n">
-        <v>45.89</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="M9" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>591396</v>
+      <c r="V9" t="n">
+        <v>10.36</v>
       </c>
     </row>
     <row r="10">
@@ -4498,37 +7194,58 @@
         <v>9.960000000000001</v>
       </c>
       <c r="E10" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.58</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>45207</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>113581</v>
+      </c>
+      <c r="K10" t="n">
+        <v>158788</v>
+      </c>
+      <c r="L10" t="n">
+        <v>51</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="U10" t="n">
         <v>58.34</v>
       </c>
-      <c r="H10" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="K10" t="n">
-        <v>37.32</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>899041</v>
+      <c r="V10" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="11">
@@ -4551,35 +7268,58 @@
         <v>48.28</v>
       </c>
       <c r="E11" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.8</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>10689</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
+        <v>3481</v>
+      </c>
+      <c r="K11" t="n">
+        <v>14170</v>
+      </c>
+      <c r="L11" t="n">
+        <v>54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v/>
+      </c>
+      <c r="R11" t="n">
+        <v/>
+      </c>
+      <c r="S11" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="n">
         <v>44.57</v>
       </c>
-      <c r="H11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="M11" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>50351</v>
+      <c r="V11" t="n">
+        <v>9.91</v>
       </c>
     </row>
     <row r="12">
@@ -4602,37 +7342,58 @@
         <v>13.23</v>
       </c>
       <c r="E12" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.66</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>3569</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
+        <v>9027</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12596</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="T12" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="U12" t="n">
         <v>14.5</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I12" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="K12" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>61449</v>
+      <c r="V12" t="n">
+        <v>3.48</v>
       </c>
     </row>
     <row r="13">
@@ -4655,35 +7416,58 @@
         <v>37.46</v>
       </c>
       <c r="E13" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.26</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
+        <v>22782</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67915</v>
+      </c>
+      <c r="L13" t="n">
+        <v>94</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v/>
+      </c>
+      <c r="R13" t="n">
+        <v/>
+      </c>
+      <c r="S13" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="T13" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="U13" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>437928</v>
+      <c r="V13" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="14">
@@ -4706,37 +7490,58 @@
         <v>20.64</v>
       </c>
       <c r="E14" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>970</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
+        <v>283</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L14" t="n">
+        <v>844</v>
+      </c>
+      <c r="M14" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="T14" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="U14" t="n">
         <v>58.43</v>
       </c>
-      <c r="H14" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M14" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>16727</v>
+      <c r="V14" t="n">
+        <v>6.47</v>
       </c>
     </row>
     <row r="15">
@@ -4759,37 +7564,58 @@
         <v>20.78</v>
       </c>
       <c r="E15" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.05</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
+        <v>1769</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2724</v>
+      </c>
+      <c r="L15" t="n">
+        <v>34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="N15" t="n">
+        <v>47</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R15" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="U15" t="n">
         <v>36.12</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="K15" t="n">
-        <v>62.19</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="M15" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>12383</v>
+      <c r="V15" t="n">
+        <v>12.3</v>
       </c>
     </row>
     <row r="16">
@@ -4812,37 +7638,58 @@
         <v>9.57</v>
       </c>
       <c r="E16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.53</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>9789</v>
       </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
+        <v>14267</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24056</v>
+      </c>
+      <c r="L16" t="n">
+        <v>45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="R16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="T16" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="U16" t="n">
         <v>56.45</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="K16" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M16" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>215962</v>
+      <c r="V16" t="n">
+        <v>9.32</v>
       </c>
     </row>
     <row r="17">
@@ -4865,37 +7712,58 @@
         <v>13.27</v>
       </c>
       <c r="E17" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.48</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>8644</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>32141</v>
+      </c>
+      <c r="K17" t="n">
+        <v>40785</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="T17" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="U17" t="n">
         <v>30.8</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I17" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="J17" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="K17" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>178501</v>
+      <c r="V17" t="n">
+        <v>5.24</v>
       </c>
     </row>
     <row r="18">
@@ -4918,37 +7786,58 @@
         <v>29.79</v>
       </c>
       <c r="E18" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.09</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>20117</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>5093</v>
+      </c>
+      <c r="K18" t="n">
+        <v>25210</v>
+      </c>
+      <c r="L18" t="n">
+        <v>63</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N18" t="n">
+        <v/>
+      </c>
+      <c r="O18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="R18" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="U18" t="n">
         <v>35.99</v>
       </c>
-      <c r="H18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="K18" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M18" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>153670</v>
+      <c r="V18" t="n">
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -4971,37 +7860,58 @@
         <v>8.369999999999999</v>
       </c>
       <c r="E19" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.08</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
+        <v>1418</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3347</v>
+      </c>
+      <c r="L19" t="n">
+        <v>480</v>
+      </c>
+      <c r="M19" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="S19" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="T19" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="U19" t="n">
         <v>25.87</v>
       </c>
-      <c r="H19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="J19" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="K19" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M19" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>20521</v>
+      <c r="V19" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="20">
@@ -5024,37 +7934,58 @@
         <v>10.36</v>
       </c>
       <c r="E20" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F20" t="n">
         <v>2.61</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>27809</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
+        <v>51089</v>
+      </c>
+      <c r="K20" t="n">
+        <v>78898</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N20" t="n">
+        <v>62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="R20" t="n">
+        <v>67.03</v>
+      </c>
+      <c r="S20" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="T20" t="n">
+        <v>100</v>
+      </c>
+      <c r="U20" t="n">
         <v>63.78</v>
       </c>
-      <c r="H20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I20" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="K20" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="M20" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>149982</v>
+      <c r="V20" t="n">
+        <v>6.28</v>
       </c>
     </row>
     <row r="21">
@@ -5077,37 +8008,58 @@
         <v>15.09</v>
       </c>
       <c r="E21" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.05</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
+        <v>763</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12135</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="R21" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" t="n">
         <v>37.9</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24.54</v>
-      </c>
-      <c r="K21" t="n">
-        <v>63.91</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M21" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>48497</v>
+      <c r="V21" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="22">
@@ -5130,37 +8082,58 @@
         <v>27.85</v>
       </c>
       <c r="E22" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>15616</v>
       </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
+        <v>1563</v>
+      </c>
+      <c r="K22" t="n">
+        <v>17179</v>
+      </c>
+      <c r="L22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="N22" t="n">
+        <v>84</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="S22" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" t="n">
         <v>47.85</v>
       </c>
-      <c r="H22" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="J22" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="K22" t="n">
-        <v>65.44</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M22" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>70866</v>
+      <c r="V22" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="23">
@@ -5183,37 +8156,58 @@
         <v>8.99</v>
       </c>
       <c r="E23" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>5058</v>
       </c>
-      <c r="G23" t="n">
+      <c r="J23" t="n">
+        <v>1318</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6376</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>150</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-10.99</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>57.4</v>
       </c>
-      <c r="H23" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-10.99</v>
-      </c>
-      <c r="K23" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M23" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>51996</v>
+      <c r="V23" t="n">
+        <v>7.43</v>
       </c>
     </row>
     <row r="24">
@@ -5236,37 +8230,58 @@
         <v>32.47</v>
       </c>
       <c r="E24" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="F24" t="n">
         <v>0.02</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
+        <v>135.83</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>5622</v>
       </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
+        <v>416</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6038</v>
+      </c>
+      <c r="L24" t="n">
+        <v>565</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="N24" t="n">
+        <v>73</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="R24" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="S24" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="T24" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="U24" t="n">
         <v>75.58</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I24" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="K24" t="n">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M24" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="N24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5849</v>
+      <c r="V24" t="n">
+        <v>4.48</v>
       </c>
     </row>
     <row r="25">
@@ -5289,37 +8304,58 @@
         <v>15.55</v>
       </c>
       <c r="E25" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="F25" t="n">
         <v>0.02</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>1152</v>
       </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
+        <v>2982</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4134</v>
+      </c>
+      <c r="L25" t="n">
+        <v>51</v>
+      </c>
+      <c r="M25" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="N25" t="n">
+        <v>25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="R25" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="S25" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="U25" t="n">
         <v>59.75</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I25" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="K25" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M25" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="N25" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>25774</v>
+      <c r="V25" t="n">
+        <v>5.93</v>
       </c>
     </row>
     <row r="26">
@@ -5342,37 +8378,58 @@
         <v>24.15</v>
       </c>
       <c r="E26" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.59</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>3106</v>
       </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
+        <v>160</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3266</v>
+      </c>
+      <c r="L26" t="n">
+        <v>49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>57</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="R26" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="T26" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="U26" t="n">
         <v>46.4</v>
       </c>
-      <c r="H26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="J26" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="K26" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M26" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="N26" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>10728</v>
+      <c r="V26" t="n">
+        <v>6.43</v>
       </c>
     </row>
   </sheetData>
